--- a/research/traditional_assets/database/data/egypt/egypt_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.171</v>
+        <v>0.173</v>
       </c>
       <c r="E2">
-        <v>0.152</v>
+        <v>0.1635</v>
       </c>
       <c r="F2">
-        <v>0.149</v>
+        <v>0.16</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0007382454896796441</v>
+        <v>0.001147676894961761</v>
       </c>
       <c r="J2">
-        <v>0.0004793911496125417</v>
+        <v>0.0007784029150654756</v>
       </c>
       <c r="K2">
-        <v>1938.7</v>
+        <v>1474.9</v>
       </c>
       <c r="L2">
-        <v>0.462807352590117</v>
+        <v>0.4732552542916734</v>
       </c>
       <c r="M2">
-        <v>204.99</v>
+        <v>392.32</v>
       </c>
       <c r="N2">
-        <v>0.0174280103042824</v>
+        <v>0.05583275221654546</v>
       </c>
       <c r="O2">
-        <v>0.1057358023417754</v>
+        <v>0.2659976947589667</v>
       </c>
       <c r="P2">
-        <v>204.99</v>
+        <v>392.32</v>
       </c>
       <c r="Q2">
-        <v>0.0174280103042824</v>
+        <v>0.05583275221654546</v>
       </c>
       <c r="R2">
-        <v>0.1057358023417754</v>
+        <v>0.2659976947589667</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>8346.1</v>
+        <v>7947.3</v>
       </c>
       <c r="V2">
-        <v>0.709575671011129</v>
+        <v>1.131014558754465</v>
       </c>
       <c r="W2">
-        <v>0.2076545877659574</v>
+        <v>0.1902733770502439</v>
       </c>
       <c r="X2">
-        <v>0.07801489738974934</v>
+        <v>0.1166653320707783</v>
       </c>
       <c r="Y2">
-        <v>0.1296396903762081</v>
+        <v>0.07360804497946562</v>
       </c>
       <c r="Z2">
-        <v>1.564555692155201</v>
+        <v>0.881035144684177</v>
       </c>
       <c r="AA2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07467694152318244</v>
+        <v>0.1128438476059752</v>
       </c>
       <c r="AC2">
-        <v>-0.07467694152318244</v>
+        <v>-0.1129325061999311</v>
       </c>
       <c r="AD2">
-        <v>1209.69</v>
+        <v>845.8000000000001</v>
       </c>
       <c r="AE2">
-        <v>60.53744821865985</v>
+        <v>38.31632478425836</v>
       </c>
       <c r="AF2">
-        <v>1270.22744821866</v>
+        <v>884.1163247842584</v>
       </c>
       <c r="AG2">
-        <v>-7075.87255178134</v>
+        <v>-7063.183675215741</v>
       </c>
       <c r="AH2">
-        <v>0.09746742884305615</v>
+        <v>0.1117604414621989</v>
       </c>
       <c r="AI2">
-        <v>0.1037222858331165</v>
+        <v>0.1133581826877261</v>
       </c>
       <c r="AJ2">
-        <v>-1.509929389891444</v>
+        <v>193.5984692728594</v>
       </c>
       <c r="AK2">
-        <v>-1.814173975319175</v>
+        <v>47.72947870715135</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>79.58486842105263</v>
+        <v>75.2491103202847</v>
       </c>
       <c r="AP2">
-        <v>-465.517931038246</v>
+        <v>-628.3971241295144</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Faisal Islamic Bank of Egypt (CASE:FAITA)</t>
+          <t>QNB Alahli S.A.E (CASE:QNBA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.175</v>
+        <v>0.179</v>
       </c>
       <c r="E3">
-        <v>0.157</v>
+        <v>0.108</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,34 +731,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.004252209114021593</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.002850361421032034</v>
       </c>
       <c r="K3">
-        <v>164.6</v>
+        <v>458.1</v>
       </c>
       <c r="L3">
-        <v>0.4487459105779716</v>
+        <v>0.5157041540020264</v>
       </c>
       <c r="M3">
-        <v>13.3</v>
+        <v>123.6</v>
       </c>
       <c r="N3">
-        <v>0.02342786683107275</v>
+        <v>0.08155724183437808</v>
       </c>
       <c r="O3">
-        <v>0.08080194410692589</v>
+        <v>0.2698100851342501</v>
       </c>
       <c r="P3">
-        <v>13.3</v>
+        <v>123.6</v>
       </c>
       <c r="Q3">
-        <v>0.02342786683107275</v>
+        <v>0.08155724183437808</v>
       </c>
       <c r="R3">
-        <v>0.08080194410692589</v>
+        <v>0.2698100851342501</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,61 +767,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1065.7</v>
+        <v>2659.4</v>
       </c>
       <c r="V3">
-        <v>1.877223885855205</v>
+        <v>1.754800395908941</v>
       </c>
       <c r="W3">
-        <v>0.1846533542741755</v>
+        <v>0.1607594048287479</v>
       </c>
       <c r="X3">
-        <v>0.07154873594235001</v>
+        <v>0.1152510593465909</v>
       </c>
       <c r="Y3">
-        <v>0.1131046183318254</v>
+        <v>0.04550834548215697</v>
       </c>
       <c r="Z3">
-        <v>-0.9463364293085655</v>
+        <v>0.4075679606212733</v>
       </c>
       <c r="AA3">
-        <v>-0</v>
+        <v>0.001161715991403581</v>
       </c>
       <c r="AB3">
-        <v>0.07129579134753541</v>
+        <v>0.1117243454165439</v>
       </c>
       <c r="AC3">
-        <v>-0.07129579134753541</v>
+        <v>-0.1105626294251403</v>
       </c>
       <c r="AD3">
-        <v>8.49</v>
+        <v>210.3</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>23.0138132200731</v>
       </c>
       <c r="AF3">
-        <v>8.49</v>
+        <v>233.3138132200731</v>
       </c>
       <c r="AG3">
-        <v>-1057.21</v>
+        <v>-2426.086186779927</v>
       </c>
       <c r="AH3">
-        <v>0.01473472292125861</v>
+        <v>0.1334126088531259</v>
       </c>
       <c r="AI3">
-        <v>0.007898482635432462</v>
+        <v>0.08281721895768913</v>
       </c>
       <c r="AJ3">
-        <v>2.15973115973116</v>
+        <v>2.664312529667519</v>
       </c>
       <c r="AK3">
-        <v>-115.0391730141451</v>
+        <v>-15.37309147581857</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>25.09546539379475</v>
+      </c>
+      <c r="AP3">
+        <v>-289.5090915011846</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Credit Agricole - Egypt Bank (S.A.E.) (CASE:CIEB)</t>
+          <t>Commercial International Bank (Egypt) S.A.E (CASE:COMI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,13 +847,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.07490000000000001</v>
+        <v>0.189</v>
       </c>
       <c r="E4">
-        <v>0.0398</v>
+        <v>0.167</v>
       </c>
       <c r="F4">
-        <v>0.09669999999999999</v>
+        <v>0.169</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,34 +862,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>-0.0001168905222626093</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>-8.086963297783402e-05</v>
       </c>
       <c r="K4">
-        <v>96.3</v>
+        <v>796.7</v>
       </c>
       <c r="L4">
-        <v>0.4373297002724796</v>
+        <v>0.4644668571095436</v>
       </c>
       <c r="M4">
-        <v>8.44</v>
+        <v>225.7</v>
       </c>
       <c r="N4">
-        <v>0.01259701492537313</v>
+        <v>0.04513638908887289</v>
       </c>
       <c r="O4">
-        <v>0.08764278296988577</v>
+        <v>0.283293586042425</v>
       </c>
       <c r="P4">
-        <v>8.44</v>
+        <v>225.7</v>
       </c>
       <c r="Q4">
-        <v>0.01259701492537313</v>
+        <v>0.04513638908887289</v>
       </c>
       <c r="R4">
-        <v>0.08764278296988577</v>
+        <v>0.283293586042425</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,61 +898,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>594.5</v>
+        <v>3752.6</v>
       </c>
       <c r="V4">
-        <v>0.8873134328358209</v>
+        <v>0.7504599632029438</v>
       </c>
       <c r="W4">
-        <v>0.2215320910973085</v>
+        <v>0.1897492080882178</v>
       </c>
       <c r="X4">
-        <v>0.07396151144518252</v>
+        <v>0.1117289335214663</v>
       </c>
       <c r="Y4">
-        <v>0.1475705796521259</v>
+        <v>0.07802027456675151</v>
       </c>
       <c r="Z4">
-        <v>-0.6255681818181817</v>
+        <v>2.192630056332455</v>
       </c>
       <c r="AA4">
-        <v>-0</v>
+        <v>-0.0001773171879117732</v>
       </c>
       <c r="AB4">
-        <v>0.0726678666286221</v>
+        <v>0.112634488002454</v>
       </c>
       <c r="AC4">
-        <v>-0.0726678666286221</v>
+        <v>-0.1128118051903658</v>
       </c>
       <c r="AD4">
-        <v>47.4</v>
+        <v>421.8</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>15.30251156418527</v>
       </c>
       <c r="AF4">
-        <v>47.4</v>
+        <v>437.1025115641853</v>
       </c>
       <c r="AG4">
-        <v>-547.1</v>
+        <v>-3315.497488435814</v>
       </c>
       <c r="AH4">
-        <v>0.06607192640089211</v>
+        <v>0.08038663166308051</v>
       </c>
       <c r="AI4">
-        <v>0.08312872676253946</v>
+        <v>0.1161208809093937</v>
       </c>
       <c r="AJ4">
-        <v>-4.451586655817739</v>
+        <v>-1.967768144257712</v>
       </c>
       <c r="AK4">
-        <v>22.51440329218101</v>
+        <v>-285.7568785942902</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>147.4825174825175</v>
+      </c>
+      <c r="AP4">
+        <v>-1159.264856096439</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QNB Alahli S.A.E (CASE:QNBA)</t>
+          <t>Housing and Development Bank- Egypt (S.A.E) (CASE:HDBK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,13 +978,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.171</v>
+        <v>0.156</v>
       </c>
       <c r="E5">
-        <v>0.147</v>
-      </c>
-      <c r="F5">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,34 +990,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.001950954911156253</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.001367310195097867</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>499.7</v>
+        <v>124.4</v>
       </c>
       <c r="L5">
-        <v>0.5252811941553663</v>
+        <v>0.464005967922417</v>
       </c>
       <c r="M5">
-        <v>54.7</v>
+        <v>34.4</v>
       </c>
       <c r="N5">
-        <v>0.02251770130083978</v>
+        <v>0.09411764705882353</v>
       </c>
       <c r="O5">
-        <v>0.1094656794076446</v>
+        <v>0.2765273311897106</v>
       </c>
       <c r="P5">
-        <v>54.7</v>
+        <v>34.4</v>
       </c>
       <c r="Q5">
-        <v>0.02251770130083978</v>
+        <v>0.09411764705882353</v>
       </c>
       <c r="R5">
-        <v>0.1094656794076446</v>
+        <v>0.2765273311897106</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,67 +1026,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>951.9</v>
+        <v>979</v>
       </c>
       <c r="V5">
-        <v>0.3918574016137</v>
+        <v>2.678522571819426</v>
       </c>
       <c r="W5">
-        <v>0.2076545877659574</v>
+        <v>0.1907975460122699</v>
       </c>
       <c r="X5">
-        <v>0.07606426021430916</v>
+        <v>0.1180796047949656</v>
       </c>
       <c r="Y5">
-        <v>0.1315903275516483</v>
+        <v>0.07271794121730434</v>
       </c>
       <c r="Z5">
-        <v>0.4855626936931001</v>
+        <v>2.156878519710379</v>
       </c>
       <c r="AA5">
-        <v>0.0006639148214457587</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07375209833305121</v>
+        <v>0.1130532072094964</v>
       </c>
       <c r="AC5">
-        <v>-0.07308818351160545</v>
+        <v>-0.1130532072094964</v>
       </c>
       <c r="AD5">
-        <v>258.8</v>
+        <v>75.8</v>
       </c>
       <c r="AE5">
-        <v>31.17028296508528</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>289.9702829650853</v>
+        <v>75.8</v>
       </c>
       <c r="AG5">
-        <v>-661.9297170349147</v>
+        <v>-903.2</v>
       </c>
       <c r="AH5">
-        <v>0.1066392512383928</v>
+        <v>0.1717652390663947</v>
       </c>
       <c r="AI5">
-        <v>0.09235986355789762</v>
+        <v>0.1111762980346143</v>
       </c>
       <c r="AJ5">
-        <v>-0.3745492262362632</v>
+        <v>1.679747070857355</v>
       </c>
       <c r="AK5">
-        <v>-0.3025728886977247</v>
+        <v>3.039030955585464</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>31.99011124845488</v>
-      </c>
-      <c r="AP5">
-        <v>-81.82073140110194</v>
       </c>
     </row>
     <row r="6">
@@ -1088,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Commercial International Bank (Egypt) S.A.E (CASE:COMI)</t>
+          <t>Abu Dhabi Islamic Bank - Egypt S.A.E. (CASE:ADIB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1097,13 +1100,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.193</v>
+        <v>0.167</v>
       </c>
       <c r="E6">
-        <v>0.179</v>
+        <v>0.264</v>
       </c>
       <c r="F6">
-        <v>0.235</v>
+        <v>0.151</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1118,28 +1121,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>812.3</v>
+        <v>95.7</v>
       </c>
       <c r="L6">
-        <v>0.4921240760935418</v>
+        <v>0.3909313725490196</v>
       </c>
       <c r="M6">
-        <v>86.59999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="N6">
-        <v>0.0130307863613109</v>
+        <v>0.05932553337921541</v>
       </c>
       <c r="O6">
-        <v>0.106610858057368</v>
+        <v>0.09007314524555902</v>
       </c>
       <c r="P6">
-        <v>86.59999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="Q6">
-        <v>0.0130307863613109</v>
+        <v>0.05932553337921541</v>
       </c>
       <c r="R6">
-        <v>0.106610858057368</v>
+        <v>0.09007314524555902</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1148,685 +1151,60 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3900.3</v>
+        <v>556.3</v>
       </c>
       <c r="V6">
-        <v>0.5868819404736826</v>
+        <v>3.828630419821059</v>
       </c>
       <c r="W6">
-        <v>0.2363260793669266</v>
+        <v>0.2474786656322731</v>
       </c>
       <c r="X6">
-        <v>0.07401249292495223</v>
+        <v>0.1573398122252337</v>
       </c>
       <c r="Y6">
-        <v>0.1623135864419744</v>
+        <v>0.09013885340703937</v>
       </c>
       <c r="Z6">
-        <v>3.133257403189066</v>
+        <v>0.5425531914893618</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07423046532619203</v>
+        <v>0.1268791580602286</v>
       </c>
       <c r="AC6">
-        <v>-0.07423046532619203</v>
+        <v>-0.1268791580602286</v>
       </c>
       <c r="AD6">
-        <v>478</v>
+        <v>137.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>478</v>
+        <v>137.9</v>
       </c>
       <c r="AG6">
-        <v>-3422.3</v>
+        <v>-418.4</v>
       </c>
       <c r="AH6">
-        <v>0.06709902018585587</v>
+        <v>0.4869350282485875</v>
       </c>
       <c r="AI6">
-        <v>0.1015789361837771</v>
+        <v>0.2572281290803954</v>
       </c>
       <c r="AJ6">
-        <v>-1.061672095548317</v>
+        <v>1.532039545953863</v>
       </c>
       <c r="AK6">
-        <v>-4.249192947603677</v>
+        <v>20.71287128712872</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Housing and Development Bank- Egypt (S.A.E) (CASE:HDBK)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.162</v>
-      </c>
-      <c r="E7">
-        <v>0.22</v>
-      </c>
-      <c r="F7">
-        <v>0.092</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>125.7</v>
-      </c>
-      <c r="L7">
-        <v>0.4436992587363219</v>
-      </c>
-      <c r="M7">
-        <v>15.7</v>
-      </c>
-      <c r="N7">
-        <v>0.0368890977443609</v>
-      </c>
-      <c r="O7">
-        <v>0.1249005568814638</v>
-      </c>
-      <c r="P7">
-        <v>15.7</v>
-      </c>
-      <c r="Q7">
-        <v>0.0368890977443609</v>
-      </c>
-      <c r="R7">
-        <v>0.1249005568814638</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>597.7</v>
-      </c>
-      <c r="V7">
-        <v>1.40437030075188</v>
-      </c>
-      <c r="W7">
-        <v>0.2540933899332929</v>
-      </c>
-      <c r="X7">
-        <v>0.07801489738974934</v>
-      </c>
-      <c r="Y7">
-        <v>0.1760784925435435</v>
-      </c>
-      <c r="Z7">
-        <v>0.8381656804733727</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.07467694152318244</v>
-      </c>
-      <c r="AC7">
-        <v>-0.07467694152318244</v>
-      </c>
-      <c r="AD7">
-        <v>70</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>70</v>
-      </c>
-      <c r="AG7">
-        <v>-527.7</v>
-      </c>
-      <c r="AH7">
-        <v>0.1412429378531073</v>
-      </c>
-      <c r="AI7">
-        <v>0.09608785175017158</v>
-      </c>
-      <c r="AJ7">
-        <v>5.168462291870714</v>
-      </c>
-      <c r="AK7">
-        <v>-4.034403669724773</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>National Bank of Kuwait - Egypt (S.A.E) (CASE:NBKE)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.147</v>
-      </c>
-      <c r="E8">
-        <v>0.121</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>-0.0004293553738852603</v>
-      </c>
-      <c r="J8">
-        <v>-0.0002878559030045221</v>
-      </c>
-      <c r="K8">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="L8">
-        <v>0.4296761720637989</v>
-      </c>
-      <c r="M8">
-        <v>9.34</v>
-      </c>
-      <c r="N8">
-        <v>0.01522164276401564</v>
-      </c>
-      <c r="O8">
-        <v>0.1050618672665917</v>
-      </c>
-      <c r="P8">
-        <v>9.34</v>
-      </c>
-      <c r="Q8">
-        <v>0.01522164276401564</v>
-      </c>
-      <c r="R8">
-        <v>0.1050618672665917</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>178.8</v>
-      </c>
-      <c r="V8">
-        <v>0.2913950456323338</v>
-      </c>
-      <c r="W8">
-        <v>0.1615188953488372</v>
-      </c>
-      <c r="X8">
-        <v>0.07838654662937715</v>
-      </c>
-      <c r="Y8">
-        <v>0.08313234871946008</v>
-      </c>
-      <c r="Z8">
-        <v>0.4513582728203245</v>
-      </c>
-      <c r="AA8">
-        <v>-0.000129926143201256</v>
-      </c>
-      <c r="AB8">
-        <v>0.0757214388183597</v>
-      </c>
-      <c r="AC8">
-        <v>-0.07585136496156096</v>
-      </c>
-      <c r="AD8">
-        <v>95</v>
-      </c>
-      <c r="AE8">
-        <v>11.1941681342843</v>
-      </c>
-      <c r="AF8">
-        <v>106.1941681342843</v>
-      </c>
-      <c r="AG8">
-        <v>-72.60583186571571</v>
-      </c>
-      <c r="AH8">
-        <v>0.1475340768730329</v>
-      </c>
-      <c r="AI8">
-        <v>0.1440127583365233</v>
-      </c>
-      <c r="AJ8">
-        <v>-0.1342081599809291</v>
-      </c>
-      <c r="AK8">
-        <v>-0.1299795737363686</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>44.18604651162791</v>
-      </c>
-      <c r="AP8">
-        <v>-33.77015435614685</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Suez Canal Bank (S.A.E) (CASE:CANA)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>0.279</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>39.6</v>
-      </c>
-      <c r="L9">
-        <v>0.323265306122449</v>
-      </c>
-      <c r="M9">
-        <v>3.57</v>
-      </c>
-      <c r="N9">
-        <v>0.02319688109161793</v>
-      </c>
-      <c r="O9">
-        <v>0.09015151515151515</v>
-      </c>
-      <c r="P9">
-        <v>3.57</v>
-      </c>
-      <c r="Q9">
-        <v>0.02319688109161793</v>
-      </c>
-      <c r="R9">
-        <v>0.09015151515151515</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>522.4</v>
-      </c>
-      <c r="V9">
-        <v>3.394411955815464</v>
-      </c>
-      <c r="W9">
-        <v>0.1741424802110818</v>
-      </c>
-      <c r="X9">
-        <v>0.08129913310278548</v>
-      </c>
-      <c r="Y9">
-        <v>0.09284334710829632</v>
-      </c>
-      <c r="Z9">
-        <v>-0.5134115674769488</v>
-      </c>
-      <c r="AA9">
-        <v>-0</v>
-      </c>
-      <c r="AB9">
-        <v>0.07677576190049323</v>
-      </c>
-      <c r="AC9">
-        <v>-0.07677576190049323</v>
-      </c>
-      <c r="AD9">
-        <v>37</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>37</v>
-      </c>
-      <c r="AG9">
-        <v>-485.4</v>
-      </c>
-      <c r="AH9">
-        <v>0.1938187532739654</v>
-      </c>
-      <c r="AI9">
-        <v>0.123497997329773</v>
-      </c>
-      <c r="AJ9">
-        <v>1.464253393665158</v>
-      </c>
-      <c r="AK9">
-        <v>2.178635547576302</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Abu Dhabi Islamic Bank - Egypt S.A.E. (CASE:ADIB)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>0.189</v>
-      </c>
-      <c r="E10">
-        <v>0.314</v>
-      </c>
-      <c r="F10">
-        <v>0.149</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0.005485929537011367</v>
-      </c>
-      <c r="J10">
-        <v>0.003612589112798283</v>
-      </c>
-      <c r="K10">
-        <v>90.2</v>
-      </c>
-      <c r="L10">
-        <v>0.3733443708609272</v>
-      </c>
-      <c r="M10">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="N10">
-        <v>0.04213147410358566</v>
-      </c>
-      <c r="O10">
-        <v>0.09379157427937916</v>
-      </c>
-      <c r="P10">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="Q10">
-        <v>0.04213147410358566</v>
-      </c>
-      <c r="R10">
-        <v>0.09379157427937916</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>41.7</v>
-      </c>
-      <c r="V10">
-        <v>0.2076693227091634</v>
-      </c>
-      <c r="W10">
-        <v>0.2755881454323251</v>
-      </c>
-      <c r="X10">
-        <v>0.09994973830124428</v>
-      </c>
-      <c r="Y10">
-        <v>0.1756384071310808</v>
-      </c>
-      <c r="Z10">
-        <v>0.6073816014402439</v>
-      </c>
-      <c r="AA10">
-        <v>0.002194220160677011</v>
-      </c>
-      <c r="AB10">
-        <v>0.08164074538075418</v>
-      </c>
-      <c r="AC10">
-        <v>-0.07944652522007717</v>
-      </c>
-      <c r="AD10">
-        <v>116.7</v>
-      </c>
-      <c r="AE10">
-        <v>18.17299711929027</v>
-      </c>
-      <c r="AF10">
-        <v>134.8729971192903</v>
-      </c>
-      <c r="AG10">
-        <v>93.17299711929026</v>
-      </c>
-      <c r="AH10">
-        <v>0.4017987692687702</v>
-      </c>
-      <c r="AI10">
-        <v>0.2455482024906437</v>
-      </c>
-      <c r="AJ10">
-        <v>0.3169440664017243</v>
-      </c>
-      <c r="AK10">
-        <v>0.183565709066656</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>23.52822580645161</v>
-      </c>
-      <c r="AP10">
-        <v>18.78487845146981</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Société Arabe Internationale de Banque S.A.E (CASE:SAIB)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>-0.0823</v>
-      </c>
-      <c r="E11">
-        <v>-0.186</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>21.4</v>
-      </c>
-      <c r="L11">
-        <v>0.1467764060356653</v>
-      </c>
-      <c r="M11">
-        <v>4.88</v>
-      </c>
-      <c r="N11">
-        <v>0.08792792792792793</v>
-      </c>
-      <c r="O11">
-        <v>0.2280373831775701</v>
-      </c>
-      <c r="P11">
-        <v>4.88</v>
-      </c>
-      <c r="Q11">
-        <v>0.08792792792792793</v>
-      </c>
-      <c r="R11">
-        <v>0.2280373831775701</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>493.1</v>
-      </c>
-      <c r="V11">
-        <v>8.884684684684686</v>
-      </c>
-      <c r="W11">
-        <v>0.06903225806451613</v>
-      </c>
-      <c r="X11">
-        <v>0.1474989962773173</v>
-      </c>
-      <c r="Y11">
-        <v>-0.07846673821280115</v>
-      </c>
-      <c r="Z11">
-        <v>-5.951020408163266</v>
-      </c>
-      <c r="AA11">
-        <v>-0</v>
-      </c>
-      <c r="AB11">
-        <v>0.08798414557922044</v>
-      </c>
-      <c r="AC11">
-        <v>-0.08798414557922044</v>
-      </c>
-      <c r="AD11">
-        <v>98.3</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>98.3</v>
-      </c>
-      <c r="AG11">
-        <v>-394.8</v>
-      </c>
-      <c r="AH11">
-        <v>0.6391417425227568</v>
-      </c>
-      <c r="AI11">
-        <v>0.2227509630636755</v>
-      </c>
-      <c r="AJ11">
-        <v>1.163572060123784</v>
-      </c>
-      <c r="AK11">
-        <v>7.62162162162162</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/egypt/egypt_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_bank_money_center.xlsx
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.173</v>
+        <v>0.233</v>
       </c>
       <c r="E2">
-        <v>0.1635</v>
-      </c>
-      <c r="F2">
-        <v>0.16</v>
+        <v>0.2535</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.001147676894961761</v>
+        <v>0.0005228214263750172</v>
       </c>
       <c r="J2">
-        <v>0.0007784029150654756</v>
+        <v>0.0003562530983571153</v>
       </c>
       <c r="K2">
-        <v>1474.9</v>
+        <v>1586</v>
       </c>
       <c r="L2">
-        <v>0.4732552542916734</v>
+        <v>0.5101646937725167</v>
       </c>
       <c r="M2">
-        <v>392.32</v>
+        <v>236.86</v>
       </c>
       <c r="N2">
-        <v>0.05583275221654546</v>
+        <v>0.02392235284611966</v>
       </c>
       <c r="O2">
-        <v>0.2659976947589667</v>
+        <v>0.149344262295082</v>
       </c>
       <c r="P2">
-        <v>392.32</v>
+        <v>236.86</v>
       </c>
       <c r="Q2">
-        <v>0.05583275221654546</v>
+        <v>0.02392235284611966</v>
       </c>
       <c r="R2">
-        <v>0.2659976947589667</v>
+        <v>0.149344262295082</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7947.3</v>
+        <v>10062.7</v>
       </c>
       <c r="V2">
-        <v>1.131014558754465</v>
+        <v>1.016311154203531</v>
       </c>
       <c r="W2">
-        <v>0.1902733770502439</v>
+        <v>0.231561112073045</v>
       </c>
       <c r="X2">
-        <v>0.1166653320707783</v>
+        <v>0.1033372583849039</v>
       </c>
       <c r="Y2">
-        <v>0.07360804497946562</v>
+        <v>0.1282238536881411</v>
       </c>
       <c r="Z2">
-        <v>0.881035144684177</v>
+        <v>4.893286195434632</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.06274252138100063</v>
       </c>
       <c r="AB2">
-        <v>0.1128438476059752</v>
+        <v>0.1040892405639498</v>
       </c>
       <c r="AC2">
-        <v>-0.1129325061999311</v>
+        <v>-0.04034439437222467</v>
       </c>
       <c r="AD2">
-        <v>845.8000000000001</v>
+        <v>636.9</v>
       </c>
       <c r="AE2">
-        <v>38.31632478425836</v>
+        <v>40.62326374842674</v>
       </c>
       <c r="AF2">
-        <v>884.1163247842584</v>
+        <v>677.5232637484268</v>
       </c>
       <c r="AG2">
-        <v>-7063.183675215741</v>
+        <v>-9385.176736251575</v>
       </c>
       <c r="AH2">
-        <v>0.1117604414621989</v>
+        <v>0.0640458443667006</v>
       </c>
       <c r="AI2">
-        <v>0.1133581826877261</v>
+        <v>0.1136989408590294</v>
       </c>
       <c r="AJ2">
-        <v>193.5984692728594</v>
+        <v>-18.18750702841777</v>
       </c>
       <c r="AK2">
-        <v>47.72947870715135</v>
+        <v>2.286960850804977</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>75.2491103202847</v>
+        <v>65.32307692307693</v>
       </c>
       <c r="AP2">
-        <v>-628.3971241295144</v>
+        <v>-962.5822293591359</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>QNB Alahli S.A.E (CASE:QNBA)</t>
+          <t>Suez Canal Bank (S.A.E) (CASE:CANA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.179</v>
+        <v>0.308</v>
       </c>
       <c r="E3">
-        <v>0.108</v>
+        <v>0.34</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,34 +728,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.004252209114021593</v>
+        <v>0.0003754011386289949</v>
       </c>
       <c r="J3">
-        <v>0.002850361421032034</v>
+        <v>0.0002321446121636773</v>
       </c>
       <c r="K3">
-        <v>458.1</v>
+        <v>53.8</v>
       </c>
       <c r="L3">
-        <v>0.5157041540020264</v>
+        <v>0.3642518618821937</v>
       </c>
       <c r="M3">
-        <v>123.6</v>
+        <v>3.86</v>
       </c>
       <c r="N3">
-        <v>0.08155724183437808</v>
+        <v>0.02161254199328107</v>
       </c>
       <c r="O3">
-        <v>0.2698100851342501</v>
+        <v>0.07174721189591078</v>
       </c>
       <c r="P3">
-        <v>123.6</v>
+        <v>3.86</v>
       </c>
       <c r="Q3">
-        <v>0.08155724183437808</v>
+        <v>0.02161254199328107</v>
       </c>
       <c r="R3">
-        <v>0.2698100851342501</v>
+        <v>0.07174721189591078</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,55 +764,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2659.4</v>
+        <v>12.5</v>
       </c>
       <c r="V3">
-        <v>1.754800395908941</v>
+        <v>0.06998880179171332</v>
       </c>
       <c r="W3">
-        <v>0.1607594048287479</v>
+        <v>0.2047184170471842</v>
       </c>
       <c r="X3">
-        <v>0.1152510593465909</v>
+        <v>0.1098278503183018</v>
       </c>
       <c r="Y3">
-        <v>0.04550834548215697</v>
-      </c>
-      <c r="Z3">
-        <v>0.4075679606212733</v>
-      </c>
-      <c r="AA3">
-        <v>0.001161715991403581</v>
+        <v>0.09489056672888241</v>
       </c>
       <c r="AB3">
-        <v>0.1117243454165439</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1105626294251403</v>
+        <v>0.107850398690894</v>
       </c>
       <c r="AD3">
-        <v>210.3</v>
+        <v>30.7</v>
       </c>
       <c r="AE3">
-        <v>23.0138132200731</v>
+        <v>5.972766259122487</v>
       </c>
       <c r="AF3">
-        <v>233.3138132200731</v>
+        <v>36.67276625912248</v>
       </c>
       <c r="AG3">
-        <v>-2426.086186779927</v>
+        <v>24.17276625912248</v>
       </c>
       <c r="AH3">
-        <v>0.1334126088531259</v>
+        <v>0.1703548799804045</v>
       </c>
       <c r="AI3">
-        <v>0.08281721895768913</v>
+        <v>0.1419923857644714</v>
       </c>
       <c r="AJ3">
-        <v>2.664312529667519</v>
+        <v>0.1192111085974544</v>
       </c>
       <c r="AK3">
-        <v>-15.37309147581857</v>
+        <v>0.09835412860038657</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>25.09546539379475</v>
+        <v>24.56</v>
       </c>
       <c r="AP3">
-        <v>-289.5090915011846</v>
+        <v>19.33821300729799</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Commercial International Bank (Egypt) S.A.E (CASE:COMI)</t>
+          <t>QNB Alahli S.A.E (CASE:QNBA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,13 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.189</v>
+        <v>0.187</v>
       </c>
       <c r="E4">
-        <v>0.167</v>
-      </c>
-      <c r="F4">
-        <v>0.169</v>
+        <v>0.185</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,34 +847,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.0001168905222626093</v>
+        <v>0.003122736699065497</v>
       </c>
       <c r="J4">
-        <v>-8.086963297783402e-05</v>
+        <v>0.002084310721377315</v>
       </c>
       <c r="K4">
-        <v>796.7</v>
+        <v>503</v>
       </c>
       <c r="L4">
-        <v>0.4644668571095436</v>
+        <v>0.563774938354629</v>
       </c>
       <c r="M4">
-        <v>225.7</v>
+        <v>88</v>
       </c>
       <c r="N4">
-        <v>0.04513638908887289</v>
+        <v>0.04483619503744841</v>
       </c>
       <c r="O4">
-        <v>0.283293586042425</v>
+        <v>0.1749502982107356</v>
       </c>
       <c r="P4">
-        <v>225.7</v>
+        <v>88</v>
       </c>
       <c r="Q4">
-        <v>0.04513638908887289</v>
+        <v>0.04483619503744841</v>
       </c>
       <c r="R4">
-        <v>0.283293586042425</v>
+        <v>0.1749502982107356</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3752.6</v>
+        <v>1827.4</v>
       </c>
       <c r="V4">
-        <v>0.7504599632029438</v>
+        <v>0.9310643501299231</v>
       </c>
       <c r="W4">
-        <v>0.1897492080882178</v>
+        <v>0.1946669762761717</v>
       </c>
       <c r="X4">
-        <v>0.1117289335214663</v>
+        <v>0.1035419646108737</v>
       </c>
       <c r="Y4">
-        <v>0.07802027456675151</v>
+        <v>0.091125011665298</v>
       </c>
       <c r="Z4">
-        <v>2.192630056332455</v>
+        <v>60.20457577413438</v>
       </c>
       <c r="AA4">
-        <v>-0.0001773171879117732</v>
+        <v>0.1254850427620013</v>
       </c>
       <c r="AB4">
-        <v>0.112634488002454</v>
+        <v>0.1031800291148287</v>
       </c>
       <c r="AC4">
-        <v>-0.1128118051903658</v>
+        <v>0.02230501364717261</v>
       </c>
       <c r="AD4">
-        <v>421.8</v>
+        <v>126.2</v>
       </c>
       <c r="AE4">
-        <v>15.30251156418527</v>
+        <v>17.01947158546882</v>
       </c>
       <c r="AF4">
-        <v>437.1025115641853</v>
+        <v>143.2194715854688</v>
       </c>
       <c r="AG4">
-        <v>-3315.497488435814</v>
+        <v>-1684.180528414531</v>
       </c>
       <c r="AH4">
-        <v>0.08038663166308051</v>
+        <v>0.0680080475620676</v>
       </c>
       <c r="AI4">
-        <v>0.1161208809093937</v>
+        <v>0.06589895018102797</v>
       </c>
       <c r="AJ4">
-        <v>-1.967768144257712</v>
+        <v>-6.046904077576167</v>
       </c>
       <c r="AK4">
-        <v>-285.7568785942902</v>
+        <v>-4.868706929665881</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -955,10 +940,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>147.4825174825175</v>
+        <v>20.38772213247173</v>
       </c>
       <c r="AP4">
-        <v>-1159.264856096439</v>
+        <v>-272.080860810102</v>
       </c>
     </row>
     <row r="5">
@@ -978,10 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.156</v>
+        <v>0.21</v>
       </c>
       <c r="E5">
-        <v>0.16</v>
+        <v>0.242</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -996,28 +981,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>124.4</v>
+        <v>176.7</v>
       </c>
       <c r="L5">
-        <v>0.464005967922417</v>
+        <v>0.5528785982478097</v>
       </c>
       <c r="M5">
-        <v>34.4</v>
+        <v>28.7</v>
       </c>
       <c r="N5">
-        <v>0.09411764705882353</v>
+        <v>0.04303493777177988</v>
       </c>
       <c r="O5">
-        <v>0.2765273311897106</v>
+        <v>0.1624221844934918</v>
       </c>
       <c r="P5">
-        <v>34.4</v>
+        <v>28.7</v>
       </c>
       <c r="Q5">
-        <v>0.09411764705882353</v>
+        <v>0.04303493777177988</v>
       </c>
       <c r="R5">
-        <v>0.2765273311897106</v>
+        <v>0.1624221844934918</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1026,55 +1011,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>979</v>
+        <v>41.5</v>
       </c>
       <c r="V5">
-        <v>2.678522571819426</v>
+        <v>0.06222822012295696</v>
       </c>
       <c r="W5">
-        <v>0.1907975460122699</v>
+        <v>0.2945490915152525</v>
       </c>
       <c r="X5">
-        <v>0.1180796047949656</v>
+        <v>0.1030104509706462</v>
       </c>
       <c r="Y5">
-        <v>0.07271794121730434</v>
+        <v>0.1915386405446064</v>
       </c>
       <c r="Z5">
-        <v>2.156878519710379</v>
+        <v>0.515068493150685</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1130532072094964</v>
+        <v>0.1029938023916219</v>
       </c>
       <c r="AC5">
-        <v>-0.1130532072094964</v>
+        <v>-0.1029938023916219</v>
       </c>
       <c r="AD5">
-        <v>75.8</v>
+        <v>41.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>75.8</v>
+        <v>41.2</v>
       </c>
       <c r="AG5">
-        <v>-903.2</v>
+        <v>-0.2999999999999972</v>
       </c>
       <c r="AH5">
-        <v>0.1717652390663947</v>
+        <v>0.05818387233441605</v>
       </c>
       <c r="AI5">
-        <v>0.1111762980346143</v>
+        <v>0.07289455060155697</v>
       </c>
       <c r="AJ5">
-        <v>1.679747070857355</v>
+        <v>-0.0004500450045004457</v>
       </c>
       <c r="AK5">
-        <v>3.039030955585464</v>
+        <v>-0.0005728470498376878</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1091,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Abu Dhabi Islamic Bank - Egypt S.A.E. (CASE:ADIB)</t>
+          <t>Commercial International Bank (Egypt) S.A.E. (CASE:COMI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,13 +1085,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.167</v>
+        <v>0.256</v>
       </c>
       <c r="E6">
-        <v>0.264</v>
-      </c>
-      <c r="F6">
-        <v>0.151</v>
+        <v>0.265</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1115,34 +1097,34 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>-0.0006952524900057651</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>-0.0004853092750362612</v>
       </c>
       <c r="K6">
-        <v>95.7</v>
+        <v>852.5</v>
       </c>
       <c r="L6">
-        <v>0.3909313725490196</v>
+        <v>0.487337792259761</v>
       </c>
       <c r="M6">
-        <v>8.619999999999999</v>
+        <v>116.3</v>
       </c>
       <c r="N6">
-        <v>0.05932553337921541</v>
+        <v>0.01639644720146623</v>
       </c>
       <c r="O6">
-        <v>0.09007314524555902</v>
+        <v>0.1364222873900293</v>
       </c>
       <c r="P6">
-        <v>8.619999999999999</v>
+        <v>116.3</v>
       </c>
       <c r="Q6">
-        <v>0.05932553337921541</v>
+        <v>0.01639644720146623</v>
       </c>
       <c r="R6">
-        <v>0.09007314524555902</v>
+        <v>0.1364222873900293</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1151,61 +1133,58 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>556.3</v>
+        <v>8181.3</v>
       </c>
       <c r="V6">
-        <v>3.828630419821059</v>
+        <v>1.153432962075285</v>
       </c>
       <c r="W6">
-        <v>0.2474786656322731</v>
+        <v>0.2584038070989058</v>
       </c>
       <c r="X6">
-        <v>0.1573398122252337</v>
+        <v>0.1031325521589341</v>
       </c>
       <c r="Y6">
-        <v>0.09013885340703937</v>
-      </c>
-      <c r="Z6">
-        <v>0.5425531914893618</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
+        <v>0.1552712549399716</v>
       </c>
       <c r="AB6">
-        <v>0.1268791580602286</v>
-      </c>
-      <c r="AC6">
-        <v>-0.1268791580602286</v>
+        <v>0.1049984520130709</v>
       </c>
       <c r="AD6">
-        <v>137.9</v>
+        <v>438.8</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>17.63102590383543</v>
       </c>
       <c r="AF6">
-        <v>137.9</v>
+        <v>456.4310259038355</v>
       </c>
       <c r="AG6">
-        <v>-418.4</v>
+        <v>-7724.868974096164</v>
       </c>
       <c r="AH6">
-        <v>0.4869350282485875</v>
+        <v>0.06045899675587677</v>
       </c>
       <c r="AI6">
-        <v>0.2572281290803954</v>
+        <v>0.1540887360864007</v>
       </c>
       <c r="AJ6">
-        <v>1.532039545953863</v>
+        <v>12.22542851569179</v>
       </c>
       <c r="AK6">
-        <v>20.71287128712872</v>
+        <v>1.480095588480909</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>189.9567099567099</v>
+      </c>
+      <c r="AP6">
+        <v>-3344.099122985353</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/egypt/egypt_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.233</v>
+        <v>0.351</v>
       </c>
       <c r="E2">
-        <v>0.2535</v>
+        <v>0.349</v>
+      </c>
+      <c r="F2">
+        <v>0.24</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0005228214263750172</v>
+        <v>0.001372350911649829</v>
       </c>
       <c r="J2">
-        <v>0.0003562530983571153</v>
+        <v>0.0009912227318694153</v>
       </c>
       <c r="K2">
-        <v>1586</v>
+        <v>1026.9</v>
       </c>
       <c r="L2">
-        <v>0.5101646937725167</v>
+        <v>0.4937019230769231</v>
       </c>
       <c r="M2">
-        <v>236.86</v>
+        <v>109</v>
       </c>
       <c r="N2">
-        <v>0.02392235284611966</v>
+        <v>0.02319346327347008</v>
       </c>
       <c r="O2">
-        <v>0.149344262295082</v>
+        <v>0.1061447073717012</v>
       </c>
       <c r="P2">
-        <v>236.86</v>
+        <v>109</v>
       </c>
       <c r="Q2">
-        <v>0.02392235284611966</v>
+        <v>0.02319346327347008</v>
       </c>
       <c r="R2">
-        <v>0.149344262295082</v>
+        <v>0.1061447073717012</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +639,46 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>10062.7</v>
+        <v>6303.2</v>
       </c>
       <c r="V2">
-        <v>1.016311154203531</v>
+        <v>1.341220529406758</v>
       </c>
       <c r="W2">
-        <v>0.231561112073045</v>
+        <v>0.4105136917849291</v>
       </c>
       <c r="X2">
-        <v>0.1033372583849039</v>
+        <v>0.1073249446141448</v>
       </c>
       <c r="Y2">
-        <v>0.1282238536881411</v>
-      </c>
-      <c r="Z2">
-        <v>4.893286195434632</v>
-      </c>
-      <c r="AA2">
-        <v>0.06274252138100063</v>
+        <v>0.3031887471707843</v>
       </c>
       <c r="AB2">
-        <v>0.1040892405639498</v>
-      </c>
-      <c r="AC2">
-        <v>-0.04034439437222467</v>
+        <v>0.1094026013583793</v>
       </c>
       <c r="AD2">
-        <v>636.9</v>
+        <v>523.5</v>
       </c>
       <c r="AE2">
-        <v>40.62326374842674</v>
+        <v>21.87755051884178</v>
       </c>
       <c r="AF2">
-        <v>677.5232637484268</v>
+        <v>545.3775505188418</v>
       </c>
       <c r="AG2">
-        <v>-9385.176736251575</v>
+        <v>-5757.822449481158</v>
       </c>
       <c r="AH2">
-        <v>0.0640458443667006</v>
+        <v>0.1039809122662293</v>
       </c>
       <c r="AI2">
-        <v>0.1136989408590294</v>
+        <v>0.1598373842458274</v>
       </c>
       <c r="AJ2">
-        <v>-18.18750702841777</v>
+        <v>5.441032225600765</v>
       </c>
       <c r="AK2">
-        <v>2.286960850804977</v>
+        <v>1.991552606329233</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>65.32307692307693</v>
+        <v>72.40663900414937</v>
       </c>
       <c r="AP2">
-        <v>-962.5822293591359</v>
+        <v>-796.3793152809347</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Suez Canal Bank (S.A.E) (CASE:CANA)</t>
+          <t>Commercial International Bank (Egypt) S.A.E (CASE:COMI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,10 +710,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.308</v>
+        <v>0.351</v>
       </c>
       <c r="E3">
-        <v>0.34</v>
+        <v>0.349</v>
+      </c>
+      <c r="F3">
+        <v>0.24</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,34 +725,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.0003754011386289949</v>
+        <v>0.001372350911649829</v>
       </c>
       <c r="J3">
-        <v>0.0002321446121636773</v>
+        <v>0.0009912227318694153</v>
       </c>
       <c r="K3">
-        <v>53.8</v>
+        <v>1026.9</v>
       </c>
       <c r="L3">
-        <v>0.3642518618821937</v>
+        <v>0.4937019230769231</v>
       </c>
       <c r="M3">
-        <v>3.86</v>
+        <v>109</v>
       </c>
       <c r="N3">
-        <v>0.02161254199328107</v>
+        <v>0.02319346327347008</v>
       </c>
       <c r="O3">
-        <v>0.07174721189591078</v>
+        <v>0.1061447073717012</v>
       </c>
       <c r="P3">
-        <v>3.86</v>
+        <v>109</v>
       </c>
       <c r="Q3">
-        <v>0.02161254199328107</v>
+        <v>0.02319346327347008</v>
       </c>
       <c r="R3">
-        <v>0.07174721189591078</v>
+        <v>0.1061447073717012</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,46 +761,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>12.5</v>
+        <v>6303.2</v>
       </c>
       <c r="V3">
-        <v>0.06998880179171332</v>
+        <v>1.341220529406758</v>
       </c>
       <c r="W3">
-        <v>0.2047184170471842</v>
+        <v>0.4105136917849291</v>
       </c>
       <c r="X3">
-        <v>0.1098278503183018</v>
+        <v>0.1073249446141448</v>
       </c>
       <c r="Y3">
-        <v>0.09489056672888241</v>
+        <v>0.3031887471707843</v>
       </c>
       <c r="AB3">
-        <v>0.107850398690894</v>
+        <v>0.1094026013583793</v>
       </c>
       <c r="AD3">
-        <v>30.7</v>
+        <v>523.5</v>
       </c>
       <c r="AE3">
-        <v>5.972766259122487</v>
+        <v>21.87755051884178</v>
       </c>
       <c r="AF3">
-        <v>36.67276625912248</v>
+        <v>545.3775505188418</v>
       </c>
       <c r="AG3">
-        <v>24.17276625912248</v>
+        <v>-5757.822449481158</v>
       </c>
       <c r="AH3">
-        <v>0.1703548799804045</v>
+        <v>0.1039809122662293</v>
       </c>
       <c r="AI3">
-        <v>0.1419923857644714</v>
+        <v>0.1598373842458274</v>
       </c>
       <c r="AJ3">
-        <v>0.1192111085974544</v>
+        <v>5.441032225600765</v>
       </c>
       <c r="AK3">
-        <v>0.09835412860038657</v>
+        <v>1.991552606329233</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -812,379 +809,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>24.56</v>
+        <v>72.40663900414937</v>
       </c>
       <c r="AP3">
-        <v>19.33821300729799</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>QNB Alahli S.A.E (CASE:QNBA)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.187</v>
-      </c>
-      <c r="E4">
-        <v>0.185</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0.003122736699065497</v>
-      </c>
-      <c r="J4">
-        <v>0.002084310721377315</v>
-      </c>
-      <c r="K4">
-        <v>503</v>
-      </c>
-      <c r="L4">
-        <v>0.563774938354629</v>
-      </c>
-      <c r="M4">
-        <v>88</v>
-      </c>
-      <c r="N4">
-        <v>0.04483619503744841</v>
-      </c>
-      <c r="O4">
-        <v>0.1749502982107356</v>
-      </c>
-      <c r="P4">
-        <v>88</v>
-      </c>
-      <c r="Q4">
-        <v>0.04483619503744841</v>
-      </c>
-      <c r="R4">
-        <v>0.1749502982107356</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>1827.4</v>
-      </c>
-      <c r="V4">
-        <v>0.9310643501299231</v>
-      </c>
-      <c r="W4">
-        <v>0.1946669762761717</v>
-      </c>
-      <c r="X4">
-        <v>0.1035419646108737</v>
-      </c>
-      <c r="Y4">
-        <v>0.091125011665298</v>
-      </c>
-      <c r="Z4">
-        <v>60.20457577413438</v>
-      </c>
-      <c r="AA4">
-        <v>0.1254850427620013</v>
-      </c>
-      <c r="AB4">
-        <v>0.1031800291148287</v>
-      </c>
-      <c r="AC4">
-        <v>0.02230501364717261</v>
-      </c>
-      <c r="AD4">
-        <v>126.2</v>
-      </c>
-      <c r="AE4">
-        <v>17.01947158546882</v>
-      </c>
-      <c r="AF4">
-        <v>143.2194715854688</v>
-      </c>
-      <c r="AG4">
-        <v>-1684.180528414531</v>
-      </c>
-      <c r="AH4">
-        <v>0.0680080475620676</v>
-      </c>
-      <c r="AI4">
-        <v>0.06589895018102797</v>
-      </c>
-      <c r="AJ4">
-        <v>-6.046904077576167</v>
-      </c>
-      <c r="AK4">
-        <v>-4.868706929665881</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>20.38772213247173</v>
-      </c>
-      <c r="AP4">
-        <v>-272.080860810102</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Housing and Development Bank- Egypt (S.A.E) (CASE:HDBK)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.21</v>
-      </c>
-      <c r="E5">
-        <v>0.242</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>176.7</v>
-      </c>
-      <c r="L5">
-        <v>0.5528785982478097</v>
-      </c>
-      <c r="M5">
-        <v>28.7</v>
-      </c>
-      <c r="N5">
-        <v>0.04303493777177988</v>
-      </c>
-      <c r="O5">
-        <v>0.1624221844934918</v>
-      </c>
-      <c r="P5">
-        <v>28.7</v>
-      </c>
-      <c r="Q5">
-        <v>0.04303493777177988</v>
-      </c>
-      <c r="R5">
-        <v>0.1624221844934918</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>41.5</v>
-      </c>
-      <c r="V5">
-        <v>0.06222822012295696</v>
-      </c>
-      <c r="W5">
-        <v>0.2945490915152525</v>
-      </c>
-      <c r="X5">
-        <v>0.1030104509706462</v>
-      </c>
-      <c r="Y5">
-        <v>0.1915386405446064</v>
-      </c>
-      <c r="Z5">
-        <v>0.515068493150685</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.1029938023916219</v>
-      </c>
-      <c r="AC5">
-        <v>-0.1029938023916219</v>
-      </c>
-      <c r="AD5">
-        <v>41.2</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>41.2</v>
-      </c>
-      <c r="AG5">
-        <v>-0.2999999999999972</v>
-      </c>
-      <c r="AH5">
-        <v>0.05818387233441605</v>
-      </c>
-      <c r="AI5">
-        <v>0.07289455060155697</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.0004500450045004457</v>
-      </c>
-      <c r="AK5">
-        <v>-0.0005728470498376878</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Commercial International Bank (Egypt) S.A.E. (CASE:COMI)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.256</v>
-      </c>
-      <c r="E6">
-        <v>0.265</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>-0.0006952524900057651</v>
-      </c>
-      <c r="J6">
-        <v>-0.0004853092750362612</v>
-      </c>
-      <c r="K6">
-        <v>852.5</v>
-      </c>
-      <c r="L6">
-        <v>0.487337792259761</v>
-      </c>
-      <c r="M6">
-        <v>116.3</v>
-      </c>
-      <c r="N6">
-        <v>0.01639644720146623</v>
-      </c>
-      <c r="O6">
-        <v>0.1364222873900293</v>
-      </c>
-      <c r="P6">
-        <v>116.3</v>
-      </c>
-      <c r="Q6">
-        <v>0.01639644720146623</v>
-      </c>
-      <c r="R6">
-        <v>0.1364222873900293</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>8181.3</v>
-      </c>
-      <c r="V6">
-        <v>1.153432962075285</v>
-      </c>
-      <c r="W6">
-        <v>0.2584038070989058</v>
-      </c>
-      <c r="X6">
-        <v>0.1031325521589341</v>
-      </c>
-      <c r="Y6">
-        <v>0.1552712549399716</v>
-      </c>
-      <c r="AB6">
-        <v>0.1049984520130709</v>
-      </c>
-      <c r="AD6">
-        <v>438.8</v>
-      </c>
-      <c r="AE6">
-        <v>17.63102590383543</v>
-      </c>
-      <c r="AF6">
-        <v>456.4310259038355</v>
-      </c>
-      <c r="AG6">
-        <v>-7724.868974096164</v>
-      </c>
-      <c r="AH6">
-        <v>0.06045899675587677</v>
-      </c>
-      <c r="AI6">
-        <v>0.1540887360864007</v>
-      </c>
-      <c r="AJ6">
-        <v>12.22542851569179</v>
-      </c>
-      <c r="AK6">
-        <v>1.480095588480909</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>189.9567099567099</v>
-      </c>
-      <c r="AP6">
-        <v>-3344.099122985353</v>
+        <v>-796.3793152809347</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/egypt/egypt_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.351</v>
+        <v>0.346</v>
       </c>
       <c r="E2">
-        <v>0.349</v>
-      </c>
-      <c r="F2">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,82 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.001372350911649829</v>
+        <v>0.001569511561699162</v>
       </c>
       <c r="J2">
-        <v>0.0009912227318694153</v>
+        <v>0.001157043798871179</v>
       </c>
       <c r="K2">
-        <v>1026.9</v>
+        <v>861.8</v>
       </c>
       <c r="L2">
-        <v>0.4937019230769231</v>
+        <v>0.5924245548910427</v>
       </c>
       <c r="M2">
-        <v>109</v>
+        <v>138.67</v>
       </c>
       <c r="N2">
-        <v>0.02319346327347008</v>
+        <v>0.05670646928927782</v>
       </c>
       <c r="O2">
-        <v>0.1061447073717012</v>
+        <v>0.1609074031097703</v>
       </c>
       <c r="P2">
-        <v>109</v>
+        <v>133.49</v>
       </c>
       <c r="Q2">
-        <v>0.02319346327347008</v>
+        <v>0.05458820642839617</v>
       </c>
       <c r="R2">
-        <v>0.1061447073717012</v>
+        <v>0.1548967277790671</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.03735487127713277</v>
       </c>
       <c r="U2">
-        <v>6303.2</v>
+        <v>6247.7</v>
       </c>
       <c r="V2">
-        <v>1.341220529406758</v>
+        <v>2.554878547476895</v>
       </c>
       <c r="W2">
-        <v>0.4105136917849291</v>
+        <v>0.4128554514720139</v>
       </c>
       <c r="X2">
-        <v>0.1073249446141448</v>
+        <v>0.1117170945471174</v>
       </c>
       <c r="Y2">
-        <v>0.3031887471707843</v>
+        <v>0.3011383569248965</v>
+      </c>
+      <c r="Z2">
+        <v>1.314663184938972</v>
+      </c>
+      <c r="AA2">
+        <v>0.002304043072303457</v>
       </c>
       <c r="AB2">
-        <v>0.1094026013583793</v>
+        <v>0.1096022390579916</v>
+      </c>
+      <c r="AC2">
+        <v>-0.102904811853043</v>
       </c>
       <c r="AD2">
-        <v>523.5</v>
+        <v>318.9</v>
       </c>
       <c r="AE2">
-        <v>21.87755051884178</v>
+        <v>18.61915765598114</v>
       </c>
       <c r="AF2">
-        <v>545.3775505188418</v>
+        <v>337.5191576559811</v>
       </c>
       <c r="AG2">
-        <v>-5757.822449481158</v>
+        <v>-5910.180842344019</v>
       </c>
       <c r="AH2">
-        <v>0.1039809122662293</v>
+        <v>0.1212824155266765</v>
       </c>
       <c r="AI2">
-        <v>0.1598373842458274</v>
+        <v>0.1088448748567556</v>
       </c>
       <c r="AJ2">
-        <v>5.441032225600765</v>
+        <v>1.705787786088548</v>
       </c>
       <c r="AK2">
-        <v>1.991552606329233</v>
+        <v>1.878167288555615</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -687,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>72.40663900414937</v>
+        <v>53.08806392542035</v>
       </c>
       <c r="AP2">
-        <v>-796.3793152809347</v>
+        <v>-983.8822777333144</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Commercial International Bank (Egypt) S.A.E (CASE:COMI)</t>
+          <t>The United Bank (CASE:UBEE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -709,110 +715,482 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.351</v>
-      </c>
-      <c r="E3">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1.944996507189968E-05</v>
+      </c>
+      <c r="J3">
+        <v>1.479293118144482E-05</v>
+      </c>
+      <c r="K3">
+        <v>53.7</v>
+      </c>
+      <c r="L3">
+        <v>0.4972222222222222</v>
+      </c>
+      <c r="M3">
+        <v>5.18</v>
+      </c>
+      <c r="N3">
+        <v>0.01668276972624799</v>
+      </c>
+      <c r="O3">
+        <v>0.09646182495344506</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
+      <c r="S3">
+        <v>5.18</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>341.8</v>
+      </c>
+      <c r="V3">
+        <v>1.100805152979066</v>
+      </c>
+      <c r="X3">
+        <v>0.1196203412208313</v>
+      </c>
+      <c r="Z3">
+        <v>4408.69971207686</v>
+      </c>
+      <c r="AA3">
+        <v>0.06521759144040859</v>
+      </c>
+      <c r="AB3">
+        <v>0.1147140101906743</v>
+      </c>
+      <c r="AC3">
+        <v>-0.04949641875026572</v>
+      </c>
+      <c r="AD3">
+        <v>123.2</v>
+      </c>
+      <c r="AE3">
+        <v>0.02449701886117418</v>
+      </c>
+      <c r="AF3">
+        <v>123.2244970188612</v>
+      </c>
+      <c r="AG3">
+        <v>-218.5755029811388</v>
+      </c>
+      <c r="AH3">
+        <v>0.2841077639511392</v>
+      </c>
+      <c r="AI3">
+        <v>0.3075042777159224</v>
+      </c>
+      <c r="AJ3">
+        <v>-2.377772085457169</v>
+      </c>
+      <c r="AK3">
+        <v>-3.709416525204703</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>17600</v>
+      </c>
+      <c r="AP3">
+        <v>-31225.0718544484</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Qatar National Bank (CASE:QNBE)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.215</v>
+      </c>
+      <c r="E4">
+        <v>0.235</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0.002542896921334422</v>
+      </c>
+      <c r="J4">
+        <v>0.001659965337772947</v>
+      </c>
+      <c r="K4">
+        <v>492.2</v>
+      </c>
+      <c r="L4">
+        <v>0.6013439218081857</v>
+      </c>
+      <c r="M4">
+        <v>78.8</v>
+      </c>
+      <c r="N4">
+        <v>0.05814210875820851</v>
+      </c>
+      <c r="O4">
+        <v>0.1600975213327915</v>
+      </c>
+      <c r="P4">
+        <v>78.8</v>
+      </c>
+      <c r="Q4">
+        <v>0.05814210875820851</v>
+      </c>
+      <c r="R4">
+        <v>0.1600975213327915</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>3854.5</v>
+      </c>
+      <c r="V4">
+        <v>2.84401977421973</v>
+      </c>
+      <c r="W4">
+        <v>0.2424511107827201</v>
+      </c>
+      <c r="X4">
+        <v>0.1058105182232916</v>
+      </c>
+      <c r="Y4">
+        <v>0.1366405925594285</v>
+      </c>
+      <c r="Z4">
+        <v>2.392622868620781</v>
+      </c>
+      <c r="AA4">
+        <v>0.003971671028273374</v>
+      </c>
+      <c r="AB4">
+        <v>0.1055506149127148</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1015789438844415</v>
+      </c>
+      <c r="AD4">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AE4">
+        <v>13.19319434943888</v>
+      </c>
+      <c r="AF4">
+        <v>110.0931943494389</v>
+      </c>
+      <c r="AG4">
+        <v>-3744.406805650561</v>
+      </c>
+      <c r="AH4">
+        <v>0.07512877415696935</v>
+      </c>
+      <c r="AI4">
+        <v>0.05961316875451281</v>
+      </c>
+      <c r="AJ4">
+        <v>1.567283135603035</v>
+      </c>
+      <c r="AK4">
+        <v>1.865016742042299</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>20.52966101694916</v>
+      </c>
+      <c r="AP4">
+        <v>-793.3065266208816</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Housing and Development Bank- Egypt (S.A.E) (CASE:HDBK)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
         <v>0.349</v>
       </c>
-      <c r="F3">
-        <v>0.24</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0.001372350911649829</v>
-      </c>
-      <c r="J3">
-        <v>0.0009912227318694153</v>
-      </c>
-      <c r="K3">
-        <v>1026.9</v>
-      </c>
-      <c r="L3">
-        <v>0.4937019230769231</v>
-      </c>
-      <c r="M3">
-        <v>109</v>
-      </c>
-      <c r="N3">
-        <v>0.02319346327347008</v>
-      </c>
-      <c r="O3">
-        <v>0.1061447073717012</v>
-      </c>
-      <c r="P3">
-        <v>109</v>
-      </c>
-      <c r="Q3">
-        <v>0.02319346327347008</v>
-      </c>
-      <c r="R3">
-        <v>0.1061447073717012</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>6303.2</v>
-      </c>
-      <c r="V3">
-        <v>1.341220529406758</v>
-      </c>
-      <c r="W3">
-        <v>0.4105136917849291</v>
-      </c>
-      <c r="X3">
-        <v>0.1073249446141448</v>
-      </c>
-      <c r="Y3">
-        <v>0.3031887471707843</v>
-      </c>
-      <c r="AB3">
-        <v>0.1094026013583793</v>
-      </c>
-      <c r="AD3">
-        <v>523.5</v>
-      </c>
-      <c r="AE3">
-        <v>21.87755051884178</v>
-      </c>
-      <c r="AF3">
-        <v>545.3775505188418</v>
-      </c>
-      <c r="AG3">
-        <v>-5757.822449481158</v>
-      </c>
-      <c r="AH3">
-        <v>0.1039809122662293</v>
-      </c>
-      <c r="AI3">
-        <v>0.1598373842458274</v>
-      </c>
-      <c r="AJ3">
-        <v>5.441032225600765</v>
-      </c>
-      <c r="AK3">
-        <v>1.991552606329233</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>72.40663900414937</v>
-      </c>
-      <c r="AP3">
-        <v>-796.3793152809347</v>
+      <c r="E5">
+        <v>0.4</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>231.8</v>
+      </c>
+      <c r="L5">
+        <v>0.6202836499866203</v>
+      </c>
+      <c r="M5">
+        <v>49.5</v>
+      </c>
+      <c r="N5">
+        <v>0.08874148440301184</v>
+      </c>
+      <c r="O5">
+        <v>0.2135461604831752</v>
+      </c>
+      <c r="P5">
+        <v>49.5</v>
+      </c>
+      <c r="Q5">
+        <v>0.08874148440301184</v>
+      </c>
+      <c r="R5">
+        <v>0.2135461604831752</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>933.1</v>
+      </c>
+      <c r="V5">
+        <v>1.67282179992829</v>
+      </c>
+      <c r="W5">
+        <v>0.4461982675649663</v>
+      </c>
+      <c r="X5">
+        <v>0.1043193020168088</v>
+      </c>
+      <c r="Y5">
+        <v>0.3418789655481576</v>
+      </c>
+      <c r="Z5">
+        <v>0.7197611710323574</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.1042306798216445</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1042306798216445</v>
+      </c>
+      <c r="AD5">
+        <v>26.3</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>26.3</v>
+      </c>
+      <c r="AG5">
+        <v>-906.8000000000001</v>
+      </c>
+      <c r="AH5">
+        <v>0.04502653655196029</v>
+      </c>
+      <c r="AI5">
+        <v>0.04830119375573921</v>
+      </c>
+      <c r="AJ5">
+        <v>2.598280802292263</v>
+      </c>
+      <c r="AK5">
+        <v>2.333504889346372</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Suez Canal Bank (S.A.E) (CASE:CANA)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.346</v>
+      </c>
+      <c r="E6">
+        <v>0.55</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0.001292600274846482</v>
+      </c>
+      <c r="J6">
+        <v>0.00101003184267074</v>
+      </c>
+      <c r="K6">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="L6">
+        <v>0.544336569579288</v>
+      </c>
+      <c r="M6">
+        <v>5.19</v>
+      </c>
+      <c r="N6">
+        <v>0.02339945897204689</v>
+      </c>
+      <c r="O6">
+        <v>0.06171224732461356</v>
+      </c>
+      <c r="P6">
+        <v>5.19</v>
+      </c>
+      <c r="Q6">
+        <v>0.02339945897204689</v>
+      </c>
+      <c r="R6">
+        <v>0.06171224732461356</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1118.3</v>
+      </c>
+      <c r="V6">
+        <v>5.041929666366095</v>
+      </c>
+      <c r="W6">
+        <v>0.3795126353790614</v>
+      </c>
+      <c r="X6">
+        <v>0.1176236708709432</v>
+      </c>
+      <c r="Y6">
+        <v>0.2618889645081182</v>
+      </c>
+      <c r="Z6">
+        <v>0.6300941113408101</v>
+      </c>
+      <c r="AA6">
+        <v>0.0006364151163335405</v>
+      </c>
+      <c r="AB6">
+        <v>0.1136538632032684</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1130174480869348</v>
+      </c>
+      <c r="AD6">
+        <v>72.5</v>
+      </c>
+      <c r="AE6">
+        <v>5.401466287681092</v>
+      </c>
+      <c r="AF6">
+        <v>77.90146628768109</v>
+      </c>
+      <c r="AG6">
+        <v>-1040.398533712319</v>
+      </c>
+      <c r="AH6">
+        <v>0.2599302140647656</v>
+      </c>
+      <c r="AI6">
+        <v>0.2521887229085897</v>
+      </c>
+      <c r="AJ6">
+        <v>1.270950888458282</v>
+      </c>
+      <c r="AK6">
+        <v>1.285397107084584</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>56.640625</v>
+      </c>
+      <c r="AP6">
+        <v>-812.811354462749</v>
       </c>
     </row>
   </sheetData>
